--- a/API文本价格.xlsx
+++ b/API文本价格.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="文本模型价格" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="已彻底下线（调用会报错）" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据来源与口径" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="文本模型价格" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="已彻底下线（调用会报错）" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="数据来源与口径" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'文本模型价格'!$A$2:$I$65</definedName>
@@ -675,7 +675,7 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>TEXT 文本模型 API 价格（USD / 每 1M tokens，标准同步档）｜自动更新于 2026-07-28</t>
+          <t>TEXT 文本模型 API 价格（USD / 每 1M tokens，标准同步档）｜自动更新于 2026-08-10</t>
         </is>
       </c>
     </row>
@@ -782,17 +782,17 @@
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>$2.50</t>
+          <t>$2.00</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>$0.25</t>
+          <t>$0.20</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
         <is>
-          <t>$15.00</t>
+          <t>$12.00</t>
         </is>
       </c>
       <c r="F4" s="5" t="inlineStr">
@@ -821,17 +821,17 @@
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>$1.00</t>
+          <t>$0.20</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>$0.10</t>
+          <t>$0.02</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>$6.00</t>
+          <t>$1.20</t>
         </is>
       </c>
       <c r="F5" s="5" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>1.05M</t>
+          <t>272K</t>
         </is>
       </c>
       <c r="G9" s="6" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>1.05M</t>
+          <t>272K</t>
         </is>
       </c>
       <c r="G10" s="6" t="inlineStr">
@@ -3690,7 +3690,7 @@
     <row r="1">
       <c r="A1" s="42" t="inlineStr">
         <is>
-          <t>自动更新于 2026-07-28｜主数据源：LiteLLM model_prices_and_context_window.json</t>
+          <t>自动更新于 2026-08-10｜主数据源：LiteLLM model_prices_and_context_window.json</t>
         </is>
       </c>
     </row>

--- a/API文本价格.xlsx
+++ b/API文本价格.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="文本模型价格" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="已彻底下线（调用会报错）" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据来源与口径" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="文本模型价格" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="已彻底下线（调用会报错）" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="数据来源与口径" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'文本模型价格'!$A$2:$I$65</definedName>
@@ -675,7 +675,7 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>TEXT 文本模型 API 价格（USD / 每 1M tokens，标准同步档）｜自动更新于 2026-07-28</t>
+          <t>TEXT 文本模型 API 价格（USD / 每 1M tokens，标准同步档）｜自动更新于 2026-08-17</t>
         </is>
       </c>
     </row>
@@ -782,17 +782,17 @@
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>$2.50</t>
+          <t>$2.00</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>$0.25</t>
+          <t>$0.20</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
         <is>
-          <t>$15.00</t>
+          <t>$12.00</t>
         </is>
       </c>
       <c r="F4" s="5" t="inlineStr">
@@ -821,17 +821,17 @@
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>$1.00</t>
+          <t>$0.20</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>$0.10</t>
+          <t>$0.02</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>$6.00</t>
+          <t>$1.20</t>
         </is>
       </c>
       <c r="F5" s="5" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>1.05M</t>
+          <t>272K</t>
         </is>
       </c>
       <c r="G9" s="6" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>1.05M</t>
+          <t>272K</t>
         </is>
       </c>
       <c r="G10" s="6" t="inlineStr">
@@ -3064,7 +3064,7 @@
       </c>
       <c r="C63" s="37" t="inlineStr">
         <is>
-          <t>$2.00</t>
+          <t>$1.25</t>
         </is>
       </c>
       <c r="D63" s="37" t="inlineStr">
@@ -3074,12 +3074,12 @@
       </c>
       <c r="E63" s="37" t="inlineStr">
         <is>
-          <t>$6.00</t>
+          <t>$2.50</t>
         </is>
       </c>
       <c r="F63" s="37" t="inlineStr">
         <is>
-          <t>2M</t>
+          <t>1M</t>
         </is>
       </c>
       <c r="G63" s="38" t="inlineStr">
@@ -3103,7 +3103,7 @@
       </c>
       <c r="C64" s="37" t="inlineStr">
         <is>
-          <t>$2.00</t>
+          <t>$1.25</t>
         </is>
       </c>
       <c r="D64" s="37" t="inlineStr">
@@ -3113,12 +3113,12 @@
       </c>
       <c r="E64" s="37" t="inlineStr">
         <is>
-          <t>$6.00</t>
+          <t>$2.50</t>
         </is>
       </c>
       <c r="F64" s="37" t="inlineStr">
         <is>
-          <t>2M</t>
+          <t>1M</t>
         </is>
       </c>
       <c r="G64" s="38" t="inlineStr">
@@ -3142,7 +3142,7 @@
       </c>
       <c r="C65" s="37" t="inlineStr">
         <is>
-          <t>$2.00</t>
+          <t>$1.25</t>
         </is>
       </c>
       <c r="D65" s="37" t="inlineStr">
@@ -3152,12 +3152,12 @@
       </c>
       <c r="E65" s="37" t="inlineStr">
         <is>
-          <t>$6.00</t>
+          <t>$2.50</t>
         </is>
       </c>
       <c r="F65" s="37" t="inlineStr">
         <is>
-          <t>2M</t>
+          <t>1M</t>
         </is>
       </c>
       <c r="G65" s="38" t="inlineStr">
@@ -3690,7 +3690,7 @@
     <row r="1">
       <c r="A1" s="42" t="inlineStr">
         <is>
-          <t>自动更新于 2026-07-28｜主数据源：LiteLLM model_prices_and_context_window.json</t>
+          <t>自动更新于 2026-08-17｜主数据源：LiteLLM model_prices_and_context_window.json</t>
         </is>
       </c>
     </row>

--- a/API文本价格.xlsx
+++ b/API文本价格.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="文本模型价格" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="已彻底下线（调用会报错）" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据来源与口径" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="文本模型价格" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="已彻底下线（调用会报错）" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="数据来源与口径" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'文本模型价格'!$A$2:$I$65</definedName>
@@ -675,7 +675,7 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>TEXT 文本模型 API 价格（USD / 每 1M tokens，标准同步档）｜自动更新于 2026-07-28</t>
+          <t>TEXT 文本模型 API 价格（USD / 每 1M tokens，标准同步档）｜自动更新于 2026-08-24</t>
         </is>
       </c>
     </row>
@@ -739,22 +739,22 @@
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>$5.00</t>
+          <t>$4.00</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>$0.50</t>
+          <t>$0.40</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
         <is>
-          <t>$30.00</t>
+          <t>$20.00</t>
         </is>
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>1.05M</t>
+          <t>922K</t>
         </is>
       </c>
       <c r="G3" s="6" t="inlineStr">
@@ -782,22 +782,22 @@
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>$2.50</t>
+          <t>$2.00</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>$0.25</t>
+          <t>$0.20</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
         <is>
-          <t>$15.00</t>
+          <t>$12.00</t>
         </is>
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>1.05M</t>
+          <t>922K</t>
         </is>
       </c>
       <c r="G4" s="6" t="inlineStr">
@@ -821,22 +821,22 @@
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>$1.00</t>
+          <t>$0.20</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>$0.10</t>
+          <t>$0.02</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>$6.00</t>
+          <t>$1.20</t>
         </is>
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>1.05M</t>
+          <t>922K</t>
         </is>
       </c>
       <c r="G5" s="6" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>1.05M</t>
+          <t>272K</t>
         </is>
       </c>
       <c r="G9" s="6" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>1.05M</t>
+          <t>272K</t>
         </is>
       </c>
       <c r="G10" s="6" t="inlineStr">
@@ -1976,17 +1976,17 @@
       </c>
       <c r="C35" s="16" t="inlineStr">
         <is>
-          <t>$1.50</t>
+          <t>$0.75</t>
         </is>
       </c>
       <c r="D35" s="16" t="inlineStr">
         <is>
-          <t>$0.15</t>
+          <t>$0.075</t>
         </is>
       </c>
       <c r="E35" s="16" t="inlineStr">
         <is>
-          <t>$7.50</t>
+          <t>$3.75</t>
         </is>
       </c>
       <c r="F35" s="16" t="inlineStr">
@@ -2857,17 +2857,17 @@
       </c>
       <c r="C58" s="32" t="inlineStr">
         <is>
-          <t>$0.14</t>
+          <t>$0.44</t>
         </is>
       </c>
       <c r="D58" s="32" t="inlineStr">
         <is>
-          <t>$0.0028</t>
+          <t>$0.014</t>
         </is>
       </c>
       <c r="E58" s="32" t="inlineStr">
         <is>
-          <t>$0.28</t>
+          <t>$1.32</t>
         </is>
       </c>
       <c r="F58" s="32" t="inlineStr">
@@ -2900,17 +2900,17 @@
       </c>
       <c r="C59" s="32" t="inlineStr">
         <is>
-          <t>$0.435</t>
+          <t>$1.32</t>
         </is>
       </c>
       <c r="D59" s="32" t="inlineStr">
         <is>
-          <t>$0.003625</t>
+          <t>$0.044</t>
         </is>
       </c>
       <c r="E59" s="32" t="inlineStr">
         <is>
-          <t>$0.87</t>
+          <t>$3.96</t>
         </is>
       </c>
       <c r="F59" s="32" t="inlineStr">
@@ -3064,7 +3064,7 @@
       </c>
       <c r="C63" s="37" t="inlineStr">
         <is>
-          <t>$2.00</t>
+          <t>$1.25</t>
         </is>
       </c>
       <c r="D63" s="37" t="inlineStr">
@@ -3074,12 +3074,12 @@
       </c>
       <c r="E63" s="37" t="inlineStr">
         <is>
-          <t>$6.00</t>
+          <t>$2.50</t>
         </is>
       </c>
       <c r="F63" s="37" t="inlineStr">
         <is>
-          <t>2M</t>
+          <t>1M</t>
         </is>
       </c>
       <c r="G63" s="38" t="inlineStr">
@@ -3103,7 +3103,7 @@
       </c>
       <c r="C64" s="37" t="inlineStr">
         <is>
-          <t>$2.00</t>
+          <t>$1.25</t>
         </is>
       </c>
       <c r="D64" s="37" t="inlineStr">
@@ -3113,12 +3113,12 @@
       </c>
       <c r="E64" s="37" t="inlineStr">
         <is>
-          <t>$6.00</t>
+          <t>$2.50</t>
         </is>
       </c>
       <c r="F64" s="37" t="inlineStr">
         <is>
-          <t>2M</t>
+          <t>1M</t>
         </is>
       </c>
       <c r="G64" s="38" t="inlineStr">
@@ -3142,7 +3142,7 @@
       </c>
       <c r="C65" s="37" t="inlineStr">
         <is>
-          <t>$2.00</t>
+          <t>$1.25</t>
         </is>
       </c>
       <c r="D65" s="37" t="inlineStr">
@@ -3152,12 +3152,12 @@
       </c>
       <c r="E65" s="37" t="inlineStr">
         <is>
-          <t>$6.00</t>
+          <t>$2.50</t>
         </is>
       </c>
       <c r="F65" s="37" t="inlineStr">
         <is>
-          <t>2M</t>
+          <t>1M</t>
         </is>
       </c>
       <c r="G65" s="38" t="inlineStr">
@@ -3690,7 +3690,7 @@
     <row r="1">
       <c r="A1" s="42" t="inlineStr">
         <is>
-          <t>自动更新于 2026-07-28｜主数据源：LiteLLM model_prices_and_context_window.json</t>
+          <t>自动更新于 2026-08-24｜主数据源：LiteLLM model_prices_and_context_window.json</t>
         </is>
       </c>
     </row>

--- a/API文本价格.xlsx
+++ b/API文本价格.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="文本模型价格" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="已彻底下线（调用会报错）" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据来源与口径" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="文本模型价格" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="已彻底下线（调用会报错）" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="数据来源与口径" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'文本模型价格'!$A$2:$I$65</definedName>
@@ -675,7 +675,7 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>TEXT 文本模型 API 价格（USD / 每 1M tokens，标准同步档）｜自动更新于 2026-07-28</t>
+          <t>TEXT 文本模型 API 价格（USD / 每 1M tokens，标准同步档）｜自动更新于 2026-08-31</t>
         </is>
       </c>
     </row>
@@ -739,22 +739,22 @@
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>$5.00</t>
+          <t>$4.00</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>$0.50</t>
+          <t>$0.40</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
         <is>
-          <t>$30.00</t>
+          <t>$20.00</t>
         </is>
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>1.05M</t>
+          <t>922K</t>
         </is>
       </c>
       <c r="G3" s="6" t="inlineStr">
@@ -782,22 +782,22 @@
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>$2.50</t>
+          <t>$2.00</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>$0.25</t>
+          <t>$0.20</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
         <is>
-          <t>$15.00</t>
+          <t>$12.00</t>
         </is>
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>1.05M</t>
+          <t>922K</t>
         </is>
       </c>
       <c r="G4" s="6" t="inlineStr">
@@ -821,22 +821,22 @@
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>$1.00</t>
+          <t>$0.20</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>$0.10</t>
+          <t>$0.02</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>$6.00</t>
+          <t>$1.20</t>
         </is>
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>1.05M</t>
+          <t>922K</t>
         </is>
       </c>
       <c r="G5" s="6" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>1.05M</t>
+          <t>272K</t>
         </is>
       </c>
       <c r="G9" s="6" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>1.05M</t>
+          <t>272K</t>
         </is>
       </c>
       <c r="G10" s="6" t="inlineStr">
@@ -1976,17 +1976,17 @@
       </c>
       <c r="C35" s="16" t="inlineStr">
         <is>
-          <t>$1.50</t>
+          <t>$0.75</t>
         </is>
       </c>
       <c r="D35" s="16" t="inlineStr">
         <is>
-          <t>$0.15</t>
+          <t>$0.075</t>
         </is>
       </c>
       <c r="E35" s="16" t="inlineStr">
         <is>
-          <t>$7.50</t>
+          <t>$3.75</t>
         </is>
       </c>
       <c r="F35" s="16" t="inlineStr">
@@ -2857,17 +2857,17 @@
       </c>
       <c r="C58" s="32" t="inlineStr">
         <is>
-          <t>$0.14</t>
+          <t>$0.44</t>
         </is>
       </c>
       <c r="D58" s="32" t="inlineStr">
         <is>
-          <t>$0.0028</t>
+          <t>$0.014</t>
         </is>
       </c>
       <c r="E58" s="32" t="inlineStr">
         <is>
-          <t>$0.28</t>
+          <t>$1.32</t>
         </is>
       </c>
       <c r="F58" s="32" t="inlineStr">
@@ -2900,17 +2900,17 @@
       </c>
       <c r="C59" s="32" t="inlineStr">
         <is>
-          <t>$0.435</t>
+          <t>$1.32</t>
         </is>
       </c>
       <c r="D59" s="32" t="inlineStr">
         <is>
-          <t>$0.003625</t>
+          <t>$0.044</t>
         </is>
       </c>
       <c r="E59" s="32" t="inlineStr">
         <is>
-          <t>$0.87</t>
+          <t>$3.96</t>
         </is>
       </c>
       <c r="F59" s="32" t="inlineStr">
@@ -3064,7 +3064,7 @@
       </c>
       <c r="C63" s="37" t="inlineStr">
         <is>
-          <t>$2.00</t>
+          <t>$1.25</t>
         </is>
       </c>
       <c r="D63" s="37" t="inlineStr">
@@ -3074,12 +3074,12 @@
       </c>
       <c r="E63" s="37" t="inlineStr">
         <is>
-          <t>$6.00</t>
+          <t>$2.50</t>
         </is>
       </c>
       <c r="F63" s="37" t="inlineStr">
         <is>
-          <t>2M</t>
+          <t>1M</t>
         </is>
       </c>
       <c r="G63" s="38" t="inlineStr">
@@ -3103,7 +3103,7 @@
       </c>
       <c r="C64" s="37" t="inlineStr">
         <is>
-          <t>$2.00</t>
+          <t>$1.25</t>
         </is>
       </c>
       <c r="D64" s="37" t="inlineStr">
@@ -3113,12 +3113,12 @@
       </c>
       <c r="E64" s="37" t="inlineStr">
         <is>
-          <t>$6.00</t>
+          <t>$2.50</t>
         </is>
       </c>
       <c r="F64" s="37" t="inlineStr">
         <is>
-          <t>2M</t>
+          <t>1M</t>
         </is>
       </c>
       <c r="G64" s="38" t="inlineStr">
@@ -3142,7 +3142,7 @@
       </c>
       <c r="C65" s="37" t="inlineStr">
         <is>
-          <t>$2.00</t>
+          <t>$1.25</t>
         </is>
       </c>
       <c r="D65" s="37" t="inlineStr">
@@ -3152,12 +3152,12 @@
       </c>
       <c r="E65" s="37" t="inlineStr">
         <is>
-          <t>$6.00</t>
+          <t>$2.50</t>
         </is>
       </c>
       <c r="F65" s="37" t="inlineStr">
         <is>
-          <t>2M</t>
+          <t>1M</t>
         </is>
       </c>
       <c r="G65" s="38" t="inlineStr">
@@ -3690,7 +3690,7 @@
     <row r="1">
       <c r="A1" s="42" t="inlineStr">
         <is>
-          <t>自动更新于 2026-07-28｜主数据源：LiteLLM model_prices_and_context_window.json</t>
+          <t>自动更新于 2026-08-31｜主数据源：LiteLLM model_prices_and_context_window.json</t>
         </is>
       </c>
     </row>

--- a/API文本价格.xlsx
+++ b/API文本价格.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="文本模型价格" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="已彻底下线（调用会报错）" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据来源与口径" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="文本模型价格" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="已彻底下线（调用会报错）" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="数据来源与口径" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'文本模型价格'!$A$2:$I$65</definedName>
@@ -675,7 +675,7 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>TEXT 文本模型 API 价格（USD / 每 1M tokens，标准同步档）｜自动更新于 2026-07-28</t>
+          <t>TEXT 文本模型 API 价格（USD / 每 1M tokens，标准同步档）｜自动更新于 2026-09-07</t>
         </is>
       </c>
     </row>
@@ -739,22 +739,22 @@
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>$5.00</t>
+          <t>$4.00</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>$0.50</t>
+          <t>$0.40</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
         <is>
-          <t>$30.00</t>
+          <t>$20.00</t>
         </is>
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>1.05M</t>
+          <t>922K</t>
         </is>
       </c>
       <c r="G3" s="6" t="inlineStr">
@@ -782,22 +782,22 @@
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>$2.50</t>
+          <t>$2.00</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>$0.25</t>
+          <t>$0.20</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
         <is>
-          <t>$15.00</t>
+          <t>$12.00</t>
         </is>
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>1.05M</t>
+          <t>922K</t>
         </is>
       </c>
       <c r="G4" s="6" t="inlineStr">
@@ -821,22 +821,22 @@
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>$1.00</t>
+          <t>$0.20</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>$0.10</t>
+          <t>$0.02</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>$6.00</t>
+          <t>$1.20</t>
         </is>
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>1.05M</t>
+          <t>922K</t>
         </is>
       </c>
       <c r="G5" s="6" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>1.05M</t>
+          <t>272K</t>
         </is>
       </c>
       <c r="G9" s="6" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>1.05M</t>
+          <t>272K</t>
         </is>
       </c>
       <c r="G10" s="6" t="inlineStr">
@@ -1976,17 +1976,17 @@
       </c>
       <c r="C35" s="16" t="inlineStr">
         <is>
-          <t>$1.50</t>
+          <t>$0.75</t>
         </is>
       </c>
       <c r="D35" s="16" t="inlineStr">
         <is>
-          <t>$0.15</t>
+          <t>$0.075</t>
         </is>
       </c>
       <c r="E35" s="16" t="inlineStr">
         <is>
-          <t>$7.50</t>
+          <t>$3.75</t>
         </is>
       </c>
       <c r="F35" s="16" t="inlineStr">
@@ -2857,17 +2857,17 @@
       </c>
       <c r="C58" s="32" t="inlineStr">
         <is>
-          <t>$0.14</t>
+          <t>$0.44</t>
         </is>
       </c>
       <c r="D58" s="32" t="inlineStr">
         <is>
-          <t>$0.0028</t>
+          <t>$0.014</t>
         </is>
       </c>
       <c r="E58" s="32" t="inlineStr">
         <is>
-          <t>$0.28</t>
+          <t>$1.32</t>
         </is>
       </c>
       <c r="F58" s="32" t="inlineStr">
@@ -2900,17 +2900,17 @@
       </c>
       <c r="C59" s="32" t="inlineStr">
         <is>
-          <t>$0.435</t>
+          <t>$1.32</t>
         </is>
       </c>
       <c r="D59" s="32" t="inlineStr">
         <is>
-          <t>$0.003625</t>
+          <t>$0.044</t>
         </is>
       </c>
       <c r="E59" s="32" t="inlineStr">
         <is>
-          <t>$0.87</t>
+          <t>$3.96</t>
         </is>
       </c>
       <c r="F59" s="32" t="inlineStr">
@@ -3064,7 +3064,7 @@
       </c>
       <c r="C63" s="37" t="inlineStr">
         <is>
-          <t>$2.00</t>
+          <t>$1.25</t>
         </is>
       </c>
       <c r="D63" s="37" t="inlineStr">
@@ -3074,12 +3074,12 @@
       </c>
       <c r="E63" s="37" t="inlineStr">
         <is>
-          <t>$6.00</t>
+          <t>$2.50</t>
         </is>
       </c>
       <c r="F63" s="37" t="inlineStr">
         <is>
-          <t>2M</t>
+          <t>1M</t>
         </is>
       </c>
       <c r="G63" s="38" t="inlineStr">
@@ -3103,7 +3103,7 @@
       </c>
       <c r="C64" s="37" t="inlineStr">
         <is>
-          <t>$2.00</t>
+          <t>$1.25</t>
         </is>
       </c>
       <c r="D64" s="37" t="inlineStr">
@@ -3113,12 +3113,12 @@
       </c>
       <c r="E64" s="37" t="inlineStr">
         <is>
-          <t>$6.00</t>
+          <t>$2.50</t>
         </is>
       </c>
       <c r="F64" s="37" t="inlineStr">
         <is>
-          <t>2M</t>
+          <t>1M</t>
         </is>
       </c>
       <c r="G64" s="38" t="inlineStr">
@@ -3142,7 +3142,7 @@
       </c>
       <c r="C65" s="37" t="inlineStr">
         <is>
-          <t>$2.00</t>
+          <t>$1.25</t>
         </is>
       </c>
       <c r="D65" s="37" t="inlineStr">
@@ -3152,12 +3152,12 @@
       </c>
       <c r="E65" s="37" t="inlineStr">
         <is>
-          <t>$6.00</t>
+          <t>$2.50</t>
         </is>
       </c>
       <c r="F65" s="37" t="inlineStr">
         <is>
-          <t>2M</t>
+          <t>1M</t>
         </is>
       </c>
       <c r="G65" s="38" t="inlineStr">
@@ -3690,7 +3690,7 @@
     <row r="1">
       <c r="A1" s="42" t="inlineStr">
         <is>
-          <t>自动更新于 2026-07-28｜主数据源：LiteLLM model_prices_and_context_window.json</t>
+          <t>自动更新于 2026-09-07｜主数据源：LiteLLM model_prices_and_context_window.json</t>
         </is>
       </c>
     </row>

--- a/API文本价格.xlsx
+++ b/API文本价格.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="文本模型价格" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="已彻底下线（调用会报错）" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据来源与口径" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="文本模型价格" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="已彻底下线（调用会报错）" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="数据来源与口径" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'文本模型价格'!$A$2:$I$65</definedName>
@@ -675,7 +675,7 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>TEXT 文本模型 API 价格（USD / 每 1M tokens，标准同步档）｜自动更新于 2026-07-28</t>
+          <t>TEXT 文本模型 API 价格（USD / 每 1M tokens，标准同步档）｜自动更新于 2026-09-14</t>
         </is>
       </c>
     </row>
@@ -739,22 +739,22 @@
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>$5.00</t>
+          <t>$4.00</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>$0.50</t>
+          <t>$0.40</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
         <is>
-          <t>$30.00</t>
+          <t>$20.00</t>
         </is>
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>1.05M</t>
+          <t>922K</t>
         </is>
       </c>
       <c r="G3" s="6" t="inlineStr">
@@ -782,22 +782,22 @@
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>$2.50</t>
+          <t>$2.00</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>$0.25</t>
+          <t>$0.20</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
         <is>
-          <t>$15.00</t>
+          <t>$12.00</t>
         </is>
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>1.05M</t>
+          <t>922K</t>
         </is>
       </c>
       <c r="G4" s="6" t="inlineStr">
@@ -821,22 +821,22 @@
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>$1.00</t>
+          <t>$0.20</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>$0.10</t>
+          <t>$0.02</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>$6.00</t>
+          <t>$1.20</t>
         </is>
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>1.05M</t>
+          <t>922K</t>
         </is>
       </c>
       <c r="G5" s="6" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>1.05M</t>
+          <t>272K</t>
         </is>
       </c>
       <c r="G9" s="6" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>1.05M</t>
+          <t>272K</t>
         </is>
       </c>
       <c r="G10" s="6" t="inlineStr">
@@ -1976,17 +1976,17 @@
       </c>
       <c r="C35" s="16" t="inlineStr">
         <is>
-          <t>$1.50</t>
+          <t>$0.75</t>
         </is>
       </c>
       <c r="D35" s="16" t="inlineStr">
         <is>
-          <t>$0.15</t>
+          <t>$0.075</t>
         </is>
       </c>
       <c r="E35" s="16" t="inlineStr">
         <is>
-          <t>$7.50</t>
+          <t>$3.75</t>
         </is>
       </c>
       <c r="F35" s="16" t="inlineStr">
@@ -2857,17 +2857,17 @@
       </c>
       <c r="C58" s="32" t="inlineStr">
         <is>
-          <t>$0.14</t>
+          <t>$0.30</t>
         </is>
       </c>
       <c r="D58" s="32" t="inlineStr">
         <is>
-          <t>$0.0028</t>
+          <t>$0.006</t>
         </is>
       </c>
       <c r="E58" s="32" t="inlineStr">
         <is>
-          <t>$0.28</t>
+          <t>$1.20</t>
         </is>
       </c>
       <c r="F58" s="32" t="inlineStr">
@@ -2900,17 +2900,17 @@
       </c>
       <c r="C59" s="32" t="inlineStr">
         <is>
-          <t>$0.435</t>
+          <t>$1.32</t>
         </is>
       </c>
       <c r="D59" s="32" t="inlineStr">
         <is>
-          <t>$0.003625</t>
+          <t>$0.044</t>
         </is>
       </c>
       <c r="E59" s="32" t="inlineStr">
         <is>
-          <t>$0.87</t>
+          <t>$3.96</t>
         </is>
       </c>
       <c r="F59" s="32" t="inlineStr">
@@ -3064,7 +3064,7 @@
       </c>
       <c r="C63" s="37" t="inlineStr">
         <is>
-          <t>$2.00</t>
+          <t>$1.25</t>
         </is>
       </c>
       <c r="D63" s="37" t="inlineStr">
@@ -3074,12 +3074,12 @@
       </c>
       <c r="E63" s="37" t="inlineStr">
         <is>
-          <t>$6.00</t>
+          <t>$2.50</t>
         </is>
       </c>
       <c r="F63" s="37" t="inlineStr">
         <is>
-          <t>2M</t>
+          <t>1M</t>
         </is>
       </c>
       <c r="G63" s="38" t="inlineStr">
@@ -3103,7 +3103,7 @@
       </c>
       <c r="C64" s="37" t="inlineStr">
         <is>
-          <t>$2.00</t>
+          <t>$1.25</t>
         </is>
       </c>
       <c r="D64" s="37" t="inlineStr">
@@ -3113,12 +3113,12 @@
       </c>
       <c r="E64" s="37" t="inlineStr">
         <is>
-          <t>$6.00</t>
+          <t>$2.50</t>
         </is>
       </c>
       <c r="F64" s="37" t="inlineStr">
         <is>
-          <t>2M</t>
+          <t>1M</t>
         </is>
       </c>
       <c r="G64" s="38" t="inlineStr">
@@ -3142,7 +3142,7 @@
       </c>
       <c r="C65" s="37" t="inlineStr">
         <is>
-          <t>$2.00</t>
+          <t>$1.25</t>
         </is>
       </c>
       <c r="D65" s="37" t="inlineStr">
@@ -3152,12 +3152,12 @@
       </c>
       <c r="E65" s="37" t="inlineStr">
         <is>
-          <t>$6.00</t>
+          <t>$2.50</t>
         </is>
       </c>
       <c r="F65" s="37" t="inlineStr">
         <is>
-          <t>2M</t>
+          <t>1M</t>
         </is>
       </c>
       <c r="G65" s="38" t="inlineStr">
@@ -3690,7 +3690,7 @@
     <row r="1">
       <c r="A1" s="42" t="inlineStr">
         <is>
-          <t>自动更新于 2026-07-28｜主数据源：LiteLLM model_prices_and_context_window.json</t>
+          <t>自动更新于 2026-09-14｜主数据源：LiteLLM model_prices_and_context_window.json</t>
         </is>
       </c>
     </row>

--- a/API文本价格.xlsx
+++ b/API文本价格.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="文本模型价格" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="已彻底下线（调用会报错）" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据来源与口径" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="文本模型价格" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="已彻底下线（调用会报错）" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="数据来源与口径" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'文本模型价格'!$A$2:$I$65</definedName>
@@ -675,7 +675,7 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>TEXT 文本模型 API 价格（USD / 每 1M tokens，标准同步档）｜自动更新于 2026-07-28</t>
+          <t>TEXT 文本模型 API 价格（USD / 每 1M tokens，标准同步档）｜自动更新于 2026-09-21</t>
         </is>
       </c>
     </row>
@@ -739,22 +739,22 @@
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>$5.00</t>
+          <t>$4.00</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>$0.50</t>
+          <t>$0.40</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
         <is>
-          <t>$30.00</t>
+          <t>$20.00</t>
         </is>
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>1.05M</t>
+          <t>922K</t>
         </is>
       </c>
       <c r="G3" s="6" t="inlineStr">
@@ -782,22 +782,22 @@
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>$2.50</t>
+          <t>$2.00</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>$0.25</t>
+          <t>$0.20</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
         <is>
-          <t>$15.00</t>
+          <t>$12.00</t>
         </is>
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>1.05M</t>
+          <t>922K</t>
         </is>
       </c>
       <c r="G4" s="6" t="inlineStr">
@@ -821,22 +821,22 @@
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>$1.00</t>
+          <t>$0.20</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>$0.10</t>
+          <t>$0.02</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>$6.00</t>
+          <t>$1.20</t>
         </is>
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>1.05M</t>
+          <t>922K</t>
         </is>
       </c>
       <c r="G5" s="6" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>1.05M</t>
+          <t>272K</t>
         </is>
       </c>
       <c r="G9" s="6" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>1.05M</t>
+          <t>272K</t>
         </is>
       </c>
       <c r="G10" s="6" t="inlineStr">
@@ -1976,17 +1976,17 @@
       </c>
       <c r="C35" s="16" t="inlineStr">
         <is>
-          <t>$1.50</t>
+          <t>$0.75</t>
         </is>
       </c>
       <c r="D35" s="16" t="inlineStr">
         <is>
-          <t>$0.15</t>
+          <t>$0.075</t>
         </is>
       </c>
       <c r="E35" s="16" t="inlineStr">
         <is>
-          <t>$7.50</t>
+          <t>$3.75</t>
         </is>
       </c>
       <c r="F35" s="16" t="inlineStr">
@@ -2638,7 +2638,7 @@
       </c>
       <c r="F52" s="28" t="inlineStr">
         <is>
-          <t>200K</t>
+          <t>1M</t>
         </is>
       </c>
       <c r="G52" s="29" t="inlineStr">
@@ -2857,17 +2857,17 @@
       </c>
       <c r="C58" s="32" t="inlineStr">
         <is>
-          <t>$0.14</t>
+          <t>$0.30</t>
         </is>
       </c>
       <c r="D58" s="32" t="inlineStr">
         <is>
-          <t>$0.0028</t>
+          <t>$0.006</t>
         </is>
       </c>
       <c r="E58" s="32" t="inlineStr">
         <is>
-          <t>$0.28</t>
+          <t>$1.20</t>
         </is>
       </c>
       <c r="F58" s="32" t="inlineStr">
@@ -2900,17 +2900,17 @@
       </c>
       <c r="C59" s="32" t="inlineStr">
         <is>
-          <t>$0.435</t>
+          <t>$1.32</t>
         </is>
       </c>
       <c r="D59" s="32" t="inlineStr">
         <is>
-          <t>$0.003625</t>
+          <t>$0.044</t>
         </is>
       </c>
       <c r="E59" s="32" t="inlineStr">
         <is>
-          <t>$0.87</t>
+          <t>$3.96</t>
         </is>
       </c>
       <c r="F59" s="32" t="inlineStr">
@@ -3064,7 +3064,7 @@
       </c>
       <c r="C63" s="37" t="inlineStr">
         <is>
-          <t>$2.00</t>
+          <t>$1.25</t>
         </is>
       </c>
       <c r="D63" s="37" t="inlineStr">
@@ -3074,12 +3074,12 @@
       </c>
       <c r="E63" s="37" t="inlineStr">
         <is>
-          <t>$6.00</t>
+          <t>$2.50</t>
         </is>
       </c>
       <c r="F63" s="37" t="inlineStr">
         <is>
-          <t>2M</t>
+          <t>1M</t>
         </is>
       </c>
       <c r="G63" s="38" t="inlineStr">
@@ -3103,7 +3103,7 @@
       </c>
       <c r="C64" s="37" t="inlineStr">
         <is>
-          <t>$2.00</t>
+          <t>$1.25</t>
         </is>
       </c>
       <c r="D64" s="37" t="inlineStr">
@@ -3113,12 +3113,12 @@
       </c>
       <c r="E64" s="37" t="inlineStr">
         <is>
-          <t>$6.00</t>
+          <t>$2.50</t>
         </is>
       </c>
       <c r="F64" s="37" t="inlineStr">
         <is>
-          <t>2M</t>
+          <t>1M</t>
         </is>
       </c>
       <c r="G64" s="38" t="inlineStr">
@@ -3142,7 +3142,7 @@
       </c>
       <c r="C65" s="37" t="inlineStr">
         <is>
-          <t>$2.00</t>
+          <t>$1.25</t>
         </is>
       </c>
       <c r="D65" s="37" t="inlineStr">
@@ -3152,12 +3152,12 @@
       </c>
       <c r="E65" s="37" t="inlineStr">
         <is>
-          <t>$6.00</t>
+          <t>$2.50</t>
         </is>
       </c>
       <c r="F65" s="37" t="inlineStr">
         <is>
-          <t>2M</t>
+          <t>1M</t>
         </is>
       </c>
       <c r="G65" s="38" t="inlineStr">
@@ -3690,7 +3690,7 @@
     <row r="1">
       <c r="A1" s="42" t="inlineStr">
         <is>
-          <t>自动更新于 2026-07-28｜主数据源：LiteLLM model_prices_and_context_window.json</t>
+          <t>自动更新于 2026-09-21｜主数据源：LiteLLM model_prices_and_context_window.json</t>
         </is>
       </c>
     </row>

--- a/API文本价格.xlsx
+++ b/API文本价格.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="文本模型价格" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="已彻底下线（调用会报错）" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据来源与口径" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="文本模型价格" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="已彻底下线（调用会报错）" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="数据来源与口径" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'文本模型价格'!$A$2:$I$65</definedName>
@@ -675,7 +675,7 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>TEXT 文本模型 API 价格（USD / 每 1M tokens，标准同步档）｜自动更新于 2026-07-28</t>
+          <t>TEXT 文本模型 API 价格（USD / 每 1M tokens，标准同步档）｜自动更新于 2026-09-28</t>
         </is>
       </c>
     </row>
@@ -739,22 +739,22 @@
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>$5.00</t>
+          <t>$4.00</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>$0.50</t>
+          <t>$0.40</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
         <is>
-          <t>$30.00</t>
+          <t>$20.00</t>
         </is>
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>1.05M</t>
+          <t>922K</t>
         </is>
       </c>
       <c r="G3" s="6" t="inlineStr">
@@ -782,22 +782,22 @@
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>$2.50</t>
+          <t>$2.00</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>$0.25</t>
+          <t>$0.20</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
         <is>
-          <t>$15.00</t>
+          <t>$12.00</t>
         </is>
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>1.05M</t>
+          <t>922K</t>
         </is>
       </c>
       <c r="G4" s="6" t="inlineStr">
@@ -821,22 +821,22 @@
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>$1.00</t>
+          <t>$0.20</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>$0.10</t>
+          <t>$0.02</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>$6.00</t>
+          <t>$1.20</t>
         </is>
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>1.05M</t>
+          <t>922K</t>
         </is>
       </c>
       <c r="G5" s="6" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>1.05M</t>
+          <t>272K</t>
         </is>
       </c>
       <c r="G9" s="6" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>1.05M</t>
+          <t>272K</t>
         </is>
       </c>
       <c r="G10" s="6" t="inlineStr">
@@ -1976,17 +1976,17 @@
       </c>
       <c r="C35" s="16" t="inlineStr">
         <is>
-          <t>$1.50</t>
+          <t>$0.75</t>
         </is>
       </c>
       <c r="D35" s="16" t="inlineStr">
         <is>
-          <t>$0.15</t>
+          <t>$0.075</t>
         </is>
       </c>
       <c r="E35" s="16" t="inlineStr">
         <is>
-          <t>$7.50</t>
+          <t>$3.75</t>
         </is>
       </c>
       <c r="F35" s="16" t="inlineStr">
@@ -2638,7 +2638,7 @@
       </c>
       <c r="F52" s="28" t="inlineStr">
         <is>
-          <t>200K</t>
+          <t>1M</t>
         </is>
       </c>
       <c r="G52" s="29" t="inlineStr">
@@ -2697,22 +2697,22 @@
       </c>
       <c r="C54" s="28" t="inlineStr">
         <is>
-          <t>$15.00</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D54" s="28" t="inlineStr">
         <is>
-          <t>$1.50</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E54" s="28" t="inlineStr">
         <is>
-          <t>$75.00</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F54" s="28" t="inlineStr">
         <is>
-          <t>200K</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G54" s="29" t="inlineStr">
@@ -2736,22 +2736,22 @@
       </c>
       <c r="C55" s="28" t="inlineStr">
         <is>
-          <t>$15.00</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D55" s="28" t="inlineStr">
         <is>
-          <t>$1.50</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E55" s="28" t="inlineStr">
         <is>
-          <t>$75.00</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F55" s="28" t="inlineStr">
         <is>
-          <t>200K</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G55" s="29" t="inlineStr">
@@ -2775,22 +2775,22 @@
       </c>
       <c r="C56" s="28" t="inlineStr">
         <is>
-          <t>$3.00</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D56" s="28" t="inlineStr">
         <is>
-          <t>$0.30</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E56" s="28" t="inlineStr">
         <is>
-          <t>$15.00</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F56" s="28" t="inlineStr">
         <is>
-          <t>1M</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G56" s="29" t="inlineStr">
@@ -2857,17 +2857,17 @@
       </c>
       <c r="C58" s="32" t="inlineStr">
         <is>
-          <t>$0.14</t>
+          <t>$0.30</t>
         </is>
       </c>
       <c r="D58" s="32" t="inlineStr">
         <is>
-          <t>$0.0028</t>
+          <t>$0.006</t>
         </is>
       </c>
       <c r="E58" s="32" t="inlineStr">
         <is>
-          <t>$0.28</t>
+          <t>$1.20</t>
         </is>
       </c>
       <c r="F58" s="32" t="inlineStr">
@@ -2900,17 +2900,17 @@
       </c>
       <c r="C59" s="32" t="inlineStr">
         <is>
-          <t>$0.435</t>
+          <t>$1.32</t>
         </is>
       </c>
       <c r="D59" s="32" t="inlineStr">
         <is>
-          <t>$0.003625</t>
+          <t>$0.044</t>
         </is>
       </c>
       <c r="E59" s="32" t="inlineStr">
         <is>
-          <t>$0.87</t>
+          <t>$3.96</t>
         </is>
       </c>
       <c r="F59" s="32" t="inlineStr">
@@ -3064,7 +3064,7 @@
       </c>
       <c r="C63" s="37" t="inlineStr">
         <is>
-          <t>$2.00</t>
+          <t>$1.25</t>
         </is>
       </c>
       <c r="D63" s="37" t="inlineStr">
@@ -3074,12 +3074,12 @@
       </c>
       <c r="E63" s="37" t="inlineStr">
         <is>
-          <t>$6.00</t>
+          <t>$2.50</t>
         </is>
       </c>
       <c r="F63" s="37" t="inlineStr">
         <is>
-          <t>2M</t>
+          <t>1M</t>
         </is>
       </c>
       <c r="G63" s="38" t="inlineStr">
@@ -3103,7 +3103,7 @@
       </c>
       <c r="C64" s="37" t="inlineStr">
         <is>
-          <t>$2.00</t>
+          <t>$1.25</t>
         </is>
       </c>
       <c r="D64" s="37" t="inlineStr">
@@ -3113,12 +3113,12 @@
       </c>
       <c r="E64" s="37" t="inlineStr">
         <is>
-          <t>$6.00</t>
+          <t>$2.50</t>
         </is>
       </c>
       <c r="F64" s="37" t="inlineStr">
         <is>
-          <t>2M</t>
+          <t>1M</t>
         </is>
       </c>
       <c r="G64" s="38" t="inlineStr">
@@ -3142,7 +3142,7 @@
       </c>
       <c r="C65" s="37" t="inlineStr">
         <is>
-          <t>$2.00</t>
+          <t>$1.25</t>
         </is>
       </c>
       <c r="D65" s="37" t="inlineStr">
@@ -3152,12 +3152,12 @@
       </c>
       <c r="E65" s="37" t="inlineStr">
         <is>
-          <t>$6.00</t>
+          <t>$2.50</t>
         </is>
       </c>
       <c r="F65" s="37" t="inlineStr">
         <is>
-          <t>2M</t>
+          <t>1M</t>
         </is>
       </c>
       <c r="G65" s="38" t="inlineStr">
@@ -3690,7 +3690,7 @@
     <row r="1">
       <c r="A1" s="42" t="inlineStr">
         <is>
-          <t>自动更新于 2026-07-28｜主数据源：LiteLLM model_prices_and_context_window.json</t>
+          <t>自动更新于 2026-09-28｜主数据源：LiteLLM model_prices_and_context_window.json</t>
         </is>
       </c>
     </row>

--- a/API文本价格.xlsx
+++ b/API文本价格.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="文本模型价格" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="已彻底下线（调用会报错）" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据来源与口径" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="文本模型价格" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="已彻底下线（调用会报错）" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="数据来源与口径" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'文本模型价格'!$A$2:$I$65</definedName>
@@ -675,7 +675,7 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>TEXT 文本模型 API 价格（USD / 每 1M tokens，标准同步档）｜自动更新于 2026-07-28</t>
+          <t>TEXT 文本模型 API 价格（USD / 每 1M tokens，标准同步档）｜自动更新于 2026-10-05</t>
         </is>
       </c>
     </row>
@@ -739,22 +739,22 @@
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>$5.00</t>
+          <t>$4.00</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>$0.50</t>
+          <t>$0.40</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
         <is>
-          <t>$30.00</t>
+          <t>$20.00</t>
         </is>
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>1.05M</t>
+          <t>922K</t>
         </is>
       </c>
       <c r="G3" s="6" t="inlineStr">
@@ -782,22 +782,22 @@
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>$2.50</t>
+          <t>$2.00</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>$0.25</t>
+          <t>$0.20</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
         <is>
-          <t>$15.00</t>
+          <t>$12.00</t>
         </is>
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>1.05M</t>
+          <t>922K</t>
         </is>
       </c>
       <c r="G4" s="6" t="inlineStr">
@@ -821,22 +821,22 @@
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>$1.00</t>
+          <t>$0.20</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>$0.10</t>
+          <t>$0.02</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>$6.00</t>
+          <t>$1.20</t>
         </is>
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>1.05M</t>
+          <t>922K</t>
         </is>
       </c>
       <c r="G5" s="6" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>1.05M</t>
+          <t>272K</t>
         </is>
       </c>
       <c r="G9" s="6" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>1.05M</t>
+          <t>272K</t>
         </is>
       </c>
       <c r="G10" s="6" t="inlineStr">
@@ -1976,17 +1976,17 @@
       </c>
       <c r="C35" s="16" t="inlineStr">
         <is>
-          <t>$1.50</t>
+          <t>$0.75</t>
         </is>
       </c>
       <c r="D35" s="16" t="inlineStr">
         <is>
-          <t>$0.15</t>
+          <t>$0.075</t>
         </is>
       </c>
       <c r="E35" s="16" t="inlineStr">
         <is>
-          <t>$7.50</t>
+          <t>$3.75</t>
         </is>
       </c>
       <c r="F35" s="16" t="inlineStr">
@@ -2638,7 +2638,7 @@
       </c>
       <c r="F52" s="28" t="inlineStr">
         <is>
-          <t>200K</t>
+          <t>1M</t>
         </is>
       </c>
       <c r="G52" s="29" t="inlineStr">
@@ -2697,22 +2697,22 @@
       </c>
       <c r="C54" s="28" t="inlineStr">
         <is>
-          <t>$15.00</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D54" s="28" t="inlineStr">
         <is>
-          <t>$1.50</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E54" s="28" t="inlineStr">
         <is>
-          <t>$75.00</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F54" s="28" t="inlineStr">
         <is>
-          <t>200K</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G54" s="29" t="inlineStr">
@@ -2736,22 +2736,22 @@
       </c>
       <c r="C55" s="28" t="inlineStr">
         <is>
-          <t>$15.00</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D55" s="28" t="inlineStr">
         <is>
-          <t>$1.50</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E55" s="28" t="inlineStr">
         <is>
-          <t>$75.00</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F55" s="28" t="inlineStr">
         <is>
-          <t>200K</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G55" s="29" t="inlineStr">
@@ -2775,22 +2775,22 @@
       </c>
       <c r="C56" s="28" t="inlineStr">
         <is>
-          <t>$3.00</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D56" s="28" t="inlineStr">
         <is>
-          <t>$0.30</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E56" s="28" t="inlineStr">
         <is>
-          <t>$15.00</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F56" s="28" t="inlineStr">
         <is>
-          <t>1M</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G56" s="29" t="inlineStr">
@@ -2857,17 +2857,17 @@
       </c>
       <c r="C58" s="32" t="inlineStr">
         <is>
-          <t>$0.14</t>
+          <t>$0.30</t>
         </is>
       </c>
       <c r="D58" s="32" t="inlineStr">
         <is>
-          <t>$0.0028</t>
+          <t>$0.006</t>
         </is>
       </c>
       <c r="E58" s="32" t="inlineStr">
         <is>
-          <t>$0.28</t>
+          <t>$1.20</t>
         </is>
       </c>
       <c r="F58" s="32" t="inlineStr">
@@ -2900,17 +2900,17 @@
       </c>
       <c r="C59" s="32" t="inlineStr">
         <is>
-          <t>$0.435</t>
+          <t>$1.32</t>
         </is>
       </c>
       <c r="D59" s="32" t="inlineStr">
         <is>
-          <t>$0.003625</t>
+          <t>$0.044</t>
         </is>
       </c>
       <c r="E59" s="32" t="inlineStr">
         <is>
-          <t>$0.87</t>
+          <t>$3.96</t>
         </is>
       </c>
       <c r="F59" s="32" t="inlineStr">
@@ -3064,7 +3064,7 @@
       </c>
       <c r="C63" s="37" t="inlineStr">
         <is>
-          <t>$2.00</t>
+          <t>$1.25</t>
         </is>
       </c>
       <c r="D63" s="37" t="inlineStr">
@@ -3074,12 +3074,12 @@
       </c>
       <c r="E63" s="37" t="inlineStr">
         <is>
-          <t>$6.00</t>
+          <t>$2.50</t>
         </is>
       </c>
       <c r="F63" s="37" t="inlineStr">
         <is>
-          <t>2M</t>
+          <t>1M</t>
         </is>
       </c>
       <c r="G63" s="38" t="inlineStr">
@@ -3103,7 +3103,7 @@
       </c>
       <c r="C64" s="37" t="inlineStr">
         <is>
-          <t>$2.00</t>
+          <t>$1.25</t>
         </is>
       </c>
       <c r="D64" s="37" t="inlineStr">
@@ -3113,12 +3113,12 @@
       </c>
       <c r="E64" s="37" t="inlineStr">
         <is>
-          <t>$6.00</t>
+          <t>$2.50</t>
         </is>
       </c>
       <c r="F64" s="37" t="inlineStr">
         <is>
-          <t>2M</t>
+          <t>1M</t>
         </is>
       </c>
       <c r="G64" s="38" t="inlineStr">
@@ -3142,7 +3142,7 @@
       </c>
       <c r="C65" s="37" t="inlineStr">
         <is>
-          <t>$2.00</t>
+          <t>$1.25</t>
         </is>
       </c>
       <c r="D65" s="37" t="inlineStr">
@@ -3152,12 +3152,12 @@
       </c>
       <c r="E65" s="37" t="inlineStr">
         <is>
-          <t>$6.00</t>
+          <t>$2.50</t>
         </is>
       </c>
       <c r="F65" s="37" t="inlineStr">
         <is>
-          <t>2M</t>
+          <t>1M</t>
         </is>
       </c>
       <c r="G65" s="38" t="inlineStr">
@@ -3690,7 +3690,7 @@
     <row r="1">
       <c r="A1" s="42" t="inlineStr">
         <is>
-          <t>自动更新于 2026-07-28｜主数据源：LiteLLM model_prices_and_context_window.json</t>
+          <t>自动更新于 2026-10-05｜主数据源：LiteLLM model_prices_and_context_window.json</t>
         </is>
       </c>
     </row>

--- a/API文本价格.xlsx
+++ b/API文本价格.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="文本模型价格" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="已彻底下线（调用会报错）" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据来源与口径" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="文本模型价格" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="已彻底下线（调用会报错）" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="数据来源与口径" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'文本模型价格'!$A$2:$I$65</definedName>
@@ -675,7 +675,7 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>TEXT 文本模型 API 价格（USD / 每 1M tokens，标准同步档）｜自动更新于 2026-07-28</t>
+          <t>TEXT 文本模型 API 价格（USD / 每 1M tokens，标准同步档）｜自动更新于 2026-10-12</t>
         </is>
       </c>
     </row>
@@ -739,22 +739,22 @@
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>$5.00</t>
+          <t>$4.00</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>$0.50</t>
+          <t>$0.40</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
         <is>
-          <t>$30.00</t>
+          <t>$20.00</t>
         </is>
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>1.05M</t>
+          <t>922K</t>
         </is>
       </c>
       <c r="G3" s="6" t="inlineStr">
@@ -782,22 +782,22 @@
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>$2.50</t>
+          <t>$2.00</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>$0.25</t>
+          <t>$0.20</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
         <is>
-          <t>$15.00</t>
+          <t>$12.00</t>
         </is>
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>1.05M</t>
+          <t>922K</t>
         </is>
       </c>
       <c r="G4" s="6" t="inlineStr">
@@ -821,22 +821,22 @@
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>$1.00</t>
+          <t>$0.20</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>$0.10</t>
+          <t>$0.02</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>$6.00</t>
+          <t>$1.20</t>
         </is>
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>1.05M</t>
+          <t>922K</t>
         </is>
       </c>
       <c r="G5" s="6" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>1.05M</t>
+          <t>272K</t>
         </is>
       </c>
       <c r="G9" s="6" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>1.05M</t>
+          <t>272K</t>
         </is>
       </c>
       <c r="G10" s="6" t="inlineStr">
@@ -1976,17 +1976,17 @@
       </c>
       <c r="C35" s="16" t="inlineStr">
         <is>
-          <t>$1.50</t>
+          <t>$0.75</t>
         </is>
       </c>
       <c r="D35" s="16" t="inlineStr">
         <is>
-          <t>$0.15</t>
+          <t>$0.075</t>
         </is>
       </c>
       <c r="E35" s="16" t="inlineStr">
         <is>
-          <t>$7.50</t>
+          <t>$3.75</t>
         </is>
       </c>
       <c r="F35" s="16" t="inlineStr">
@@ -2697,22 +2697,22 @@
       </c>
       <c r="C54" s="28" t="inlineStr">
         <is>
-          <t>$15.00</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D54" s="28" t="inlineStr">
         <is>
-          <t>$1.50</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E54" s="28" t="inlineStr">
         <is>
-          <t>$75.00</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F54" s="28" t="inlineStr">
         <is>
-          <t>200K</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G54" s="29" t="inlineStr">
@@ -2736,22 +2736,22 @@
       </c>
       <c r="C55" s="28" t="inlineStr">
         <is>
-          <t>$15.00</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D55" s="28" t="inlineStr">
         <is>
-          <t>$1.50</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E55" s="28" t="inlineStr">
         <is>
-          <t>$75.00</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F55" s="28" t="inlineStr">
         <is>
-          <t>200K</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G55" s="29" t="inlineStr">
@@ -2775,22 +2775,22 @@
       </c>
       <c r="C56" s="28" t="inlineStr">
         <is>
-          <t>$3.00</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D56" s="28" t="inlineStr">
         <is>
-          <t>$0.30</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E56" s="28" t="inlineStr">
         <is>
-          <t>$15.00</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F56" s="28" t="inlineStr">
         <is>
-          <t>1M</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G56" s="29" t="inlineStr">
@@ -2857,17 +2857,17 @@
       </c>
       <c r="C58" s="32" t="inlineStr">
         <is>
-          <t>$0.14</t>
+          <t>$0.30</t>
         </is>
       </c>
       <c r="D58" s="32" t="inlineStr">
         <is>
-          <t>$0.0028</t>
+          <t>$0.006</t>
         </is>
       </c>
       <c r="E58" s="32" t="inlineStr">
         <is>
-          <t>$0.28</t>
+          <t>$1.20</t>
         </is>
       </c>
       <c r="F58" s="32" t="inlineStr">
@@ -2900,17 +2900,17 @@
       </c>
       <c r="C59" s="32" t="inlineStr">
         <is>
-          <t>$0.435</t>
+          <t>$1.32</t>
         </is>
       </c>
       <c r="D59" s="32" t="inlineStr">
         <is>
-          <t>$0.003625</t>
+          <t>$0.044</t>
         </is>
       </c>
       <c r="E59" s="32" t="inlineStr">
         <is>
-          <t>$0.87</t>
+          <t>$3.96</t>
         </is>
       </c>
       <c r="F59" s="32" t="inlineStr">
@@ -3064,7 +3064,7 @@
       </c>
       <c r="C63" s="37" t="inlineStr">
         <is>
-          <t>$2.00</t>
+          <t>$1.25</t>
         </is>
       </c>
       <c r="D63" s="37" t="inlineStr">
@@ -3074,12 +3074,12 @@
       </c>
       <c r="E63" s="37" t="inlineStr">
         <is>
-          <t>$6.00</t>
+          <t>$2.50</t>
         </is>
       </c>
       <c r="F63" s="37" t="inlineStr">
         <is>
-          <t>2M</t>
+          <t>1M</t>
         </is>
       </c>
       <c r="G63" s="38" t="inlineStr">
@@ -3103,7 +3103,7 @@
       </c>
       <c r="C64" s="37" t="inlineStr">
         <is>
-          <t>$2.00</t>
+          <t>$1.25</t>
         </is>
       </c>
       <c r="D64" s="37" t="inlineStr">
@@ -3113,12 +3113,12 @@
       </c>
       <c r="E64" s="37" t="inlineStr">
         <is>
-          <t>$6.00</t>
+          <t>$2.50</t>
         </is>
       </c>
       <c r="F64" s="37" t="inlineStr">
         <is>
-          <t>2M</t>
+          <t>1M</t>
         </is>
       </c>
       <c r="G64" s="38" t="inlineStr">
@@ -3142,7 +3142,7 @@
       </c>
       <c r="C65" s="37" t="inlineStr">
         <is>
-          <t>$2.00</t>
+          <t>$1.25</t>
         </is>
       </c>
       <c r="D65" s="37" t="inlineStr">
@@ -3152,12 +3152,12 @@
       </c>
       <c r="E65" s="37" t="inlineStr">
         <is>
-          <t>$6.00</t>
+          <t>$2.50</t>
         </is>
       </c>
       <c r="F65" s="37" t="inlineStr">
         <is>
-          <t>2M</t>
+          <t>1M</t>
         </is>
       </c>
       <c r="G65" s="38" t="inlineStr">
@@ -3690,7 +3690,7 @@
     <row r="1">
       <c r="A1" s="42" t="inlineStr">
         <is>
-          <t>自动更新于 2026-07-28｜主数据源：LiteLLM model_prices_and_context_window.json</t>
+          <t>自动更新于 2026-10-12｜主数据源：LiteLLM model_prices_and_context_window.json</t>
         </is>
       </c>
     </row>

--- a/API文本价格.xlsx
+++ b/API文本价格.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="文本模型价格" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="已彻底下线（调用会报错）" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据来源与口径" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="文本模型价格" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="已彻底下线（调用会报错）" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="数据来源与口径" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'文本模型价格'!$A$2:$I$65</definedName>
@@ -675,7 +675,7 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>TEXT 文本模型 API 价格（USD / 每 1M tokens，标准同步档）｜自动更新于 2026-07-28</t>
+          <t>TEXT 文本模型 API 价格（USD / 每 1M tokens，标准同步档）｜自动更新于 2026-10-19</t>
         </is>
       </c>
     </row>
@@ -739,22 +739,22 @@
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>$5.00</t>
+          <t>$4.00</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>$0.50</t>
+          <t>$0.40</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
         <is>
-          <t>$30.00</t>
+          <t>$20.00</t>
         </is>
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>1.05M</t>
+          <t>922K</t>
         </is>
       </c>
       <c r="G3" s="6" t="inlineStr">
@@ -782,22 +782,22 @@
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>$2.50</t>
+          <t>$2.00</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>$0.25</t>
+          <t>$0.20</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
         <is>
-          <t>$15.00</t>
+          <t>$12.00</t>
         </is>
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>1.05M</t>
+          <t>922K</t>
         </is>
       </c>
       <c r="G4" s="6" t="inlineStr">
@@ -821,22 +821,22 @@
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>$1.00</t>
+          <t>$0.20</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>$0.10</t>
+          <t>$0.02</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>$6.00</t>
+          <t>$1.20</t>
         </is>
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>1.05M</t>
+          <t>922K</t>
         </is>
       </c>
       <c r="G5" s="6" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>1.05M</t>
+          <t>272K</t>
         </is>
       </c>
       <c r="G9" s="6" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>1.05M</t>
+          <t>272K</t>
         </is>
       </c>
       <c r="G10" s="6" t="inlineStr">
@@ -1976,17 +1976,17 @@
       </c>
       <c r="C35" s="16" t="inlineStr">
         <is>
-          <t>$1.50</t>
+          <t>$0.75</t>
         </is>
       </c>
       <c r="D35" s="16" t="inlineStr">
         <is>
-          <t>$0.15</t>
+          <t>$0.075</t>
         </is>
       </c>
       <c r="E35" s="16" t="inlineStr">
         <is>
-          <t>$7.50</t>
+          <t>$3.75</t>
         </is>
       </c>
       <c r="F35" s="16" t="inlineStr">
@@ -2697,22 +2697,22 @@
       </c>
       <c r="C54" s="28" t="inlineStr">
         <is>
-          <t>$15.00</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D54" s="28" t="inlineStr">
         <is>
-          <t>$1.50</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E54" s="28" t="inlineStr">
         <is>
-          <t>$75.00</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F54" s="28" t="inlineStr">
         <is>
-          <t>200K</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G54" s="29" t="inlineStr">
@@ -2736,22 +2736,22 @@
       </c>
       <c r="C55" s="28" t="inlineStr">
         <is>
-          <t>$15.00</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D55" s="28" t="inlineStr">
         <is>
-          <t>$1.50</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E55" s="28" t="inlineStr">
         <is>
-          <t>$75.00</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F55" s="28" t="inlineStr">
         <is>
-          <t>200K</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G55" s="29" t="inlineStr">
@@ -2775,22 +2775,22 @@
       </c>
       <c r="C56" s="28" t="inlineStr">
         <is>
-          <t>$3.00</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D56" s="28" t="inlineStr">
         <is>
-          <t>$0.30</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E56" s="28" t="inlineStr">
         <is>
-          <t>$15.00</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F56" s="28" t="inlineStr">
         <is>
-          <t>1M</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G56" s="29" t="inlineStr">
@@ -2857,17 +2857,17 @@
       </c>
       <c r="C58" s="32" t="inlineStr">
         <is>
-          <t>$0.14</t>
+          <t>$0.30</t>
         </is>
       </c>
       <c r="D58" s="32" t="inlineStr">
         <is>
-          <t>$0.0028</t>
+          <t>$0.006</t>
         </is>
       </c>
       <c r="E58" s="32" t="inlineStr">
         <is>
-          <t>$0.28</t>
+          <t>$1.20</t>
         </is>
       </c>
       <c r="F58" s="32" t="inlineStr">
@@ -2900,17 +2900,17 @@
       </c>
       <c r="C59" s="32" t="inlineStr">
         <is>
-          <t>$0.435</t>
+          <t>$1.32</t>
         </is>
       </c>
       <c r="D59" s="32" t="inlineStr">
         <is>
-          <t>$0.003625</t>
+          <t>$0.044</t>
         </is>
       </c>
       <c r="E59" s="32" t="inlineStr">
         <is>
-          <t>$0.87</t>
+          <t>$3.96</t>
         </is>
       </c>
       <c r="F59" s="32" t="inlineStr">
@@ -3064,7 +3064,7 @@
       </c>
       <c r="C63" s="37" t="inlineStr">
         <is>
-          <t>$2.00</t>
+          <t>$1.25</t>
         </is>
       </c>
       <c r="D63" s="37" t="inlineStr">
@@ -3074,12 +3074,12 @@
       </c>
       <c r="E63" s="37" t="inlineStr">
         <is>
-          <t>$6.00</t>
+          <t>$2.50</t>
         </is>
       </c>
       <c r="F63" s="37" t="inlineStr">
         <is>
-          <t>2M</t>
+          <t>1M</t>
         </is>
       </c>
       <c r="G63" s="38" t="inlineStr">
@@ -3103,7 +3103,7 @@
       </c>
       <c r="C64" s="37" t="inlineStr">
         <is>
-          <t>$2.00</t>
+          <t>$1.25</t>
         </is>
       </c>
       <c r="D64" s="37" t="inlineStr">
@@ -3113,12 +3113,12 @@
       </c>
       <c r="E64" s="37" t="inlineStr">
         <is>
-          <t>$6.00</t>
+          <t>$2.50</t>
         </is>
       </c>
       <c r="F64" s="37" t="inlineStr">
         <is>
-          <t>2M</t>
+          <t>1M</t>
         </is>
       </c>
       <c r="G64" s="38" t="inlineStr">
@@ -3142,7 +3142,7 @@
       </c>
       <c r="C65" s="37" t="inlineStr">
         <is>
-          <t>$2.00</t>
+          <t>$1.25</t>
         </is>
       </c>
       <c r="D65" s="37" t="inlineStr">
@@ -3152,12 +3152,12 @@
       </c>
       <c r="E65" s="37" t="inlineStr">
         <is>
-          <t>$6.00</t>
+          <t>$2.50</t>
         </is>
       </c>
       <c r="F65" s="37" t="inlineStr">
         <is>
-          <t>2M</t>
+          <t>1M</t>
         </is>
       </c>
       <c r="G65" s="38" t="inlineStr">
@@ -3690,7 +3690,7 @@
     <row r="1">
       <c r="A1" s="42" t="inlineStr">
         <is>
-          <t>自动更新于 2026-07-28｜主数据源：LiteLLM model_prices_and_context_window.json</t>
+          <t>自动更新于 2026-10-19｜主数据源：LiteLLM model_prices_and_context_window.json</t>
         </is>
       </c>
     </row>

--- a/API文本价格.xlsx
+++ b/API文本价格.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="文本模型价格" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="已彻底下线（调用会报错）" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据来源与口径" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="文本模型价格" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="已彻底下线（调用会报错）" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="数据来源与口径" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'文本模型价格'!$A$2:$I$65</definedName>
@@ -675,7 +675,7 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>TEXT 文本模型 API 价格（USD / 每 1M tokens，标准同步档）｜自动更新于 2026-07-28</t>
+          <t>TEXT 文本模型 API 价格（USD / 每 1M tokens，标准同步档）｜自动更新于 2026-10-26</t>
         </is>
       </c>
     </row>
@@ -739,22 +739,22 @@
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>$5.00</t>
+          <t>$4.00</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>$0.50</t>
+          <t>$0.40</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
         <is>
-          <t>$30.00</t>
+          <t>$20.00</t>
         </is>
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>1.05M</t>
+          <t>922K</t>
         </is>
       </c>
       <c r="G3" s="6" t="inlineStr">
@@ -782,22 +782,22 @@
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>$2.50</t>
+          <t>$2.00</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>$0.25</t>
+          <t>$0.20</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
         <is>
-          <t>$15.00</t>
+          <t>$12.00</t>
         </is>
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>1.05M</t>
+          <t>922K</t>
         </is>
       </c>
       <c r="G4" s="6" t="inlineStr">
@@ -821,22 +821,22 @@
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>$1.00</t>
+          <t>$0.20</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>$0.10</t>
+          <t>$0.02</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>$6.00</t>
+          <t>$1.20</t>
         </is>
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>1.05M</t>
+          <t>922K</t>
         </is>
       </c>
       <c r="G5" s="6" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>1.05M</t>
+          <t>272K</t>
         </is>
       </c>
       <c r="G9" s="6" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>1.05M</t>
+          <t>272K</t>
         </is>
       </c>
       <c r="G10" s="6" t="inlineStr">
@@ -1976,17 +1976,17 @@
       </c>
       <c r="C35" s="16" t="inlineStr">
         <is>
-          <t>$1.50</t>
+          <t>$0.75</t>
         </is>
       </c>
       <c r="D35" s="16" t="inlineStr">
         <is>
-          <t>$0.15</t>
+          <t>$0.075</t>
         </is>
       </c>
       <c r="E35" s="16" t="inlineStr">
         <is>
-          <t>$7.50</t>
+          <t>$3.75</t>
         </is>
       </c>
       <c r="F35" s="16" t="inlineStr">
@@ -2697,22 +2697,22 @@
       </c>
       <c r="C54" s="28" t="inlineStr">
         <is>
-          <t>$15.00</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D54" s="28" t="inlineStr">
         <is>
-          <t>$1.50</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E54" s="28" t="inlineStr">
         <is>
-          <t>$75.00</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F54" s="28" t="inlineStr">
         <is>
-          <t>200K</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G54" s="29" t="inlineStr">
@@ -2736,22 +2736,22 @@
       </c>
       <c r="C55" s="28" t="inlineStr">
         <is>
-          <t>$15.00</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D55" s="28" t="inlineStr">
         <is>
-          <t>$1.50</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E55" s="28" t="inlineStr">
         <is>
-          <t>$75.00</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F55" s="28" t="inlineStr">
         <is>
-          <t>200K</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G55" s="29" t="inlineStr">
@@ -2775,22 +2775,22 @@
       </c>
       <c r="C56" s="28" t="inlineStr">
         <is>
-          <t>$3.00</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D56" s="28" t="inlineStr">
         <is>
-          <t>$0.30</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E56" s="28" t="inlineStr">
         <is>
-          <t>$15.00</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F56" s="28" t="inlineStr">
         <is>
-          <t>1M</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G56" s="29" t="inlineStr">
@@ -2857,17 +2857,17 @@
       </c>
       <c r="C58" s="32" t="inlineStr">
         <is>
-          <t>$0.14</t>
+          <t>$0.30</t>
         </is>
       </c>
       <c r="D58" s="32" t="inlineStr">
         <is>
-          <t>$0.0028</t>
+          <t>$0.006</t>
         </is>
       </c>
       <c r="E58" s="32" t="inlineStr">
         <is>
-          <t>$0.28</t>
+          <t>$1.20</t>
         </is>
       </c>
       <c r="F58" s="32" t="inlineStr">
@@ -2900,17 +2900,17 @@
       </c>
       <c r="C59" s="32" t="inlineStr">
         <is>
-          <t>$0.435</t>
+          <t>$1.32</t>
         </is>
       </c>
       <c r="D59" s="32" t="inlineStr">
         <is>
-          <t>$0.003625</t>
+          <t>$0.044</t>
         </is>
       </c>
       <c r="E59" s="32" t="inlineStr">
         <is>
-          <t>$0.87</t>
+          <t>$3.96</t>
         </is>
       </c>
       <c r="F59" s="32" t="inlineStr">
@@ -3064,7 +3064,7 @@
       </c>
       <c r="C63" s="37" t="inlineStr">
         <is>
-          <t>$2.00</t>
+          <t>$1.25</t>
         </is>
       </c>
       <c r="D63" s="37" t="inlineStr">
@@ -3074,12 +3074,12 @@
       </c>
       <c r="E63" s="37" t="inlineStr">
         <is>
-          <t>$6.00</t>
+          <t>$2.50</t>
         </is>
       </c>
       <c r="F63" s="37" t="inlineStr">
         <is>
-          <t>2M</t>
+          <t>1M</t>
         </is>
       </c>
       <c r="G63" s="38" t="inlineStr">
@@ -3103,7 +3103,7 @@
       </c>
       <c r="C64" s="37" t="inlineStr">
         <is>
-          <t>$2.00</t>
+          <t>$1.25</t>
         </is>
       </c>
       <c r="D64" s="37" t="inlineStr">
@@ -3113,12 +3113,12 @@
       </c>
       <c r="E64" s="37" t="inlineStr">
         <is>
-          <t>$6.00</t>
+          <t>$2.50</t>
         </is>
       </c>
       <c r="F64" s="37" t="inlineStr">
         <is>
-          <t>2M</t>
+          <t>1M</t>
         </is>
       </c>
       <c r="G64" s="38" t="inlineStr">
@@ -3142,7 +3142,7 @@
       </c>
       <c r="C65" s="37" t="inlineStr">
         <is>
-          <t>$2.00</t>
+          <t>$1.25</t>
         </is>
       </c>
       <c r="D65" s="37" t="inlineStr">
@@ -3152,12 +3152,12 @@
       </c>
       <c r="E65" s="37" t="inlineStr">
         <is>
-          <t>$6.00</t>
+          <t>$2.50</t>
         </is>
       </c>
       <c r="F65" s="37" t="inlineStr">
         <is>
-          <t>2M</t>
+          <t>1M</t>
         </is>
       </c>
       <c r="G65" s="38" t="inlineStr">
@@ -3690,7 +3690,7 @@
     <row r="1">
       <c r="A1" s="42" t="inlineStr">
         <is>
-          <t>自动更新于 2026-07-28｜主数据源：LiteLLM model_prices_and_context_window.json</t>
+          <t>自动更新于 2026-10-26｜主数据源：LiteLLM model_prices_and_context_window.json</t>
         </is>
       </c>
     </row>
